--- a/data/통신_표준품셈.xlsx
+++ b/data/통신_표준품셈.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,17 +1221,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경질비닐전선관_노출HI104mm</t>
+          <t>UTP케이블CAT.6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>경질비닐전선관_노출</t>
+          <t>UTP케이블</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HI 104 mm</t>
+          <t>CAT.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1241,35 +1241,35 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>보통인부</t>
+          <t>통신내선공</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.001</v>
+        <v>0.04</v>
       </c>
       <c r="G22" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>전기5-1</t>
+          <t>통신4-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UTP케이블CAT.6</t>
+          <t>광케이블SM4C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTP케이블</t>
+          <t>광케이블</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAT.6</t>
+          <t>SM 4C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1279,54 +1279,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>통신내선공</t>
+          <t>통신케이블공</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G23" t="n">
         <v>100</v>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>통신4-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>광케이블SM4C</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>광케이블</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SM 4C</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>통신케이블공</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G24" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" t="inlineStr">
         <is>
           <t>통신4-2</t>
         </is>
